--- a/packages/templates/files/sheet-timesheet.xlsx
+++ b/packages/templates/files/sheet-timesheet.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="B4" s="3">
         <f>TODAY()-WEEKDAY(TODAY(),3)</f>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
       </c>
       <c r="B8" s="9">
         <f>B4</f>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C8" s="18">
         <v>0.375</v>
@@ -519,7 +519,7 @@
       </c>
       <c r="B9" s="9">
         <f>B8+1</f>
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="C9" s="18">
         <v>0.375</v>
@@ -543,7 +543,7 @@
       </c>
       <c r="B10" s="9">
         <f>B9+1</f>
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="C10" s="18">
         <v>0.375</v>
@@ -567,7 +567,7 @@
       </c>
       <c r="B11" s="9">
         <f>B10+1</f>
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="C11" s="18">
         <v>0.375</v>
@@ -591,7 +591,7 @@
       </c>
       <c r="B12" s="9">
         <f>B11+1</f>
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="C12" s="18">
         <v>0.375</v>
@@ -615,7 +615,7 @@
       </c>
       <c r="B13" s="9">
         <f>B12+1</f>
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -633,7 +633,7 @@
       </c>
       <c r="B14" s="9">
         <f>B13+1</f>
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
